--- a/Team-Data/2010-11/4-3-2010-11.xlsx
+++ b/Team-Data/2010-11/4-3-2010-11.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -664,13 +731,13 @@
         <v>76</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -679,7 +746,7 @@
         <v>36.2</v>
       </c>
       <c r="J2" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>0.462</v>
@@ -688,67 +755,67 @@
         <v>6.3</v>
       </c>
       <c r="M2" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="O2" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P2" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="n">
         <v>0.78</v>
       </c>
       <c r="R2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S2" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T2" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="U2" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V2" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y2" t="n">
         <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>28</v>
@@ -760,10 +827,10 @@
         <v>25</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM2" t="n">
         <v>16</v>
@@ -772,19 +839,19 @@
         <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP2" t="n">
         <v>29</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -793,25 +860,25 @@
         <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
         <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
         <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.703</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J3" t="n">
         <v>76</v>
       </c>
       <c r="K3" t="n">
-        <v>0.488</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.366</v>
+        <v>0.364</v>
       </c>
       <c r="O3" t="n">
         <v>17.7</v>
@@ -882,13 +949,13 @@
         <v>23.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R3" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T3" t="n">
         <v>38.9</v>
@@ -903,40 +970,40 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y3" t="n">
         <v>4.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF3" t="n">
         <v>4</v>
       </c>
       <c r="AG3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH3" t="n">
         <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -954,13 +1021,13 @@
         <v>12</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
         <v>23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
@@ -972,7 +1039,7 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
         <v>19</v>
@@ -981,16 +1048,16 @@
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AY3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1110,7 @@
         <v>34.7</v>
       </c>
       <c r="J4" t="n">
-        <v>77.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K4" t="n">
         <v>0.449</v>
@@ -1061,10 +1128,10 @@
         <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R4" t="n">
         <v>10.5</v>
@@ -1076,43 +1143,43 @@
         <v>40.7</v>
       </c>
       <c r="U4" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
         <v>6.3</v>
       </c>
       <c r="X4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA4" t="n">
         <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
         <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>19</v>
@@ -1124,7 +1191,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>28</v>
@@ -1145,16 +1212,16 @@
         <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT4" t="n">
         <v>19</v>
       </c>
       <c r="AU4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
         <v>24</v>
@@ -1163,16 +1230,16 @@
         <v>28</v>
       </c>
       <c r="AX4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
         <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>0.747</v>
+        <v>0.737</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J5" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>0.461</v>
@@ -1237,7 +1304,7 @@
         <v>17.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O5" t="n">
         <v>18.2</v>
@@ -1246,16 +1313,16 @@
         <v>24.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.739</v>
+        <v>0.737</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T5" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U5" t="n">
         <v>22.1</v>
@@ -1273,61 +1340,61 @@
         <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB5" t="n">
         <v>98.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
         <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
         <v>17</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
         <v>5</v>
@@ -1339,22 +1406,22 @@
         <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
         <v>18</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
         <v>26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -1392,49 +1459,49 @@
         <v>75</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0.187</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J6" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="L6" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M6" t="n">
         <v>18.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="O6" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
         <v>25.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.741</v>
+        <v>0.744</v>
       </c>
       <c r="R6" t="n">
         <v>10.5</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T6" t="n">
         <v>40.5</v>
@@ -1443,43 +1510,43 @@
         <v>20.9</v>
       </c>
       <c r="V6" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W6" t="n">
         <v>6.7</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC6" t="n">
-        <v>-10.2</v>
+        <v>-9.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
         <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG6" t="n">
         <v>30</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
         <v>28</v>
@@ -1491,19 +1558,19 @@
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM6" t="n">
         <v>13</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
         <v>10</v>
       </c>
       <c r="AP6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
         <v>25</v>
@@ -1515,16 +1582,16 @@
         <v>23</v>
       </c>
       <c r="AT6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU6" t="n">
         <v>17</v>
       </c>
       <c r="AV6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX6" t="n">
         <v>28</v>
@@ -1533,13 +1600,13 @@
         <v>27</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -1574,61 +1641,61 @@
         <v>76</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.697</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J7" t="n">
         <v>78.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L7" t="n">
         <v>7.9</v>
       </c>
       <c r="M7" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O7" t="n">
         <v>17.5</v>
       </c>
       <c r="P7" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R7" t="n">
         <v>9.4</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U7" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V7" t="n">
         <v>13.8</v>
       </c>
       <c r="W7" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X7" t="n">
         <v>4.3</v>
@@ -1646,25 +1713,25 @@
         <v>99.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
         <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
@@ -1679,10 +1746,10 @@
         <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
         <v>27</v>
@@ -1694,19 +1761,19 @@
         <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
@@ -1721,7 +1788,7 @@
         <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -1780,37 +1847,37 @@
         <v>8.1</v>
       </c>
       <c r="M8" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.389</v>
+        <v>0.388</v>
       </c>
       <c r="O8" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.769</v>
+        <v>0.773</v>
       </c>
       <c r="R8" t="n">
         <v>9.5</v>
       </c>
       <c r="S8" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T8" t="n">
         <v>41.9</v>
       </c>
       <c r="U8" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V8" t="n">
         <v>14.1</v>
       </c>
       <c r="W8" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X8" t="n">
         <v>4.3</v>
@@ -1819,25 +1886,25 @@
         <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.3</v>
+        <v>107.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
         <v>9</v>
@@ -1849,7 +1916,7 @@
         <v>10</v>
       </c>
       <c r="AJ8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
         <v>3</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
         <v>27</v>
@@ -1879,22 +1946,22 @@
         <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ8" t="n">
         <v>19</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -1953,10 +2020,10 @@
         <v>37</v>
       </c>
       <c r="J9" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L9" t="n">
         <v>5.8</v>
@@ -1971,28 +2038,28 @@
         <v>16.3</v>
       </c>
       <c r="P9" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.734</v>
+        <v>0.73</v>
       </c>
       <c r="R9" t="n">
         <v>11.3</v>
       </c>
       <c r="S9" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="T9" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="U9" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="X9" t="n">
         <v>4</v>
@@ -2001,19 +2068,19 @@
         <v>4.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>96.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4.2</v>
+        <v>-4.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2028,7 +2095,7 @@
         <v>6</v>
       </c>
       <c r="AI9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ9" t="n">
         <v>14</v>
@@ -2046,7 +2113,7 @@
         <v>4</v>
       </c>
       <c r="AO9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
         <v>28</v>
@@ -2064,13 +2131,13 @@
         <v>30</v>
       </c>
       <c r="AU9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX9" t="n">
         <v>30</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="n">
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>0.421</v>
+        <v>0.429</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>39.4</v>
+        <v>39.6</v>
       </c>
       <c r="J10" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L10" t="n">
         <v>8.300000000000001</v>
@@ -2150,13 +2217,13 @@
         <v>0.392</v>
       </c>
       <c r="O10" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P10" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R10" t="n">
         <v>11.5</v>
@@ -2165,16 +2232,16 @@
         <v>28.8</v>
       </c>
       <c r="T10" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U10" t="n">
         <v>22.4</v>
       </c>
       <c r="V10" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X10" t="n">
         <v>4.9</v>
@@ -2183,19 +2250,19 @@
         <v>4.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA10" t="n">
         <v>18.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>102.9</v>
+        <v>103.2</v>
       </c>
       <c r="AC10" t="n">
         <v>-2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2204,10 +2271,10 @@
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
         <v>1</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
         <v>5</v>
@@ -2234,16 +2301,16 @@
         <v>30</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR10" t="n">
         <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2255,22 +2322,22 @@
         <v>2</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB10" t="n">
         <v>7</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>0.547</v>
+        <v>0.526</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J11" t="n">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L11" t="n">
         <v>8.300000000000001</v>
@@ -2329,55 +2396,55 @@
         <v>22.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O11" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="P11" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="R11" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S11" t="n">
         <v>30.9</v>
       </c>
       <c r="T11" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U11" t="n">
         <v>23.6</v>
       </c>
       <c r="V11" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W11" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y11" t="n">
         <v>5.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>105.9</v>
+        <v>106.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
@@ -2410,25 +2477,25 @@
         <v>7</v>
       </c>
       <c r="AO11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP11" t="n">
         <v>5</v>
       </c>
-      <c r="AP11" t="n">
-        <v>7</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
         <v>13</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV11" t="n">
         <v>6</v>
@@ -2437,16 +2504,16 @@
         <v>19</v>
       </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY11" t="n">
         <v>23</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -2496,28 +2563,28 @@
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J12" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L12" t="n">
         <v>7.1</v>
       </c>
       <c r="M12" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N12" t="n">
         <v>0.351</v>
       </c>
       <c r="O12" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P12" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0.784</v>
@@ -2526,7 +2593,7 @@
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T12" t="n">
         <v>43.7</v>
@@ -2535,7 +2602,7 @@
         <v>19.5</v>
       </c>
       <c r="V12" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W12" t="n">
         <v>7</v>
@@ -2544,7 +2611,7 @@
         <v>5.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z12" t="n">
         <v>21.6</v>
@@ -2553,7 +2620,7 @@
         <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC12" t="n">
         <v>-1.2</v>
@@ -2577,10 +2644,10 @@
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>10</v>
@@ -2595,7 +2662,7 @@
         <v>7</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
@@ -2628,10 +2695,10 @@
         <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
         <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J13" t="n">
         <v>80.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L13" t="n">
         <v>6.3</v>
@@ -2693,7 +2760,7 @@
         <v>18.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O13" t="n">
         <v>19.2</v>
@@ -2702,7 +2769,7 @@
         <v>27</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="R13" t="n">
         <v>11.6</v>
@@ -2717,7 +2784,7 @@
         <v>22.1</v>
       </c>
       <c r="V13" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2735,13 +2802,13 @@
         <v>22.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>23</v>
@@ -2759,7 +2826,7 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
         <v>18</v>
@@ -2801,7 +2868,7 @@
         <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
@@ -2810,13 +2877,13 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -2848,13 +2915,13 @@
         <v>75</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.72</v>
+        <v>0.733</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,49 +2930,49 @@
         <v>38.3</v>
       </c>
       <c r="J14" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L14" t="n">
         <v>6.4</v>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.353</v>
+        <v>0.356</v>
       </c>
       <c r="O14" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P14" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="R14" t="n">
         <v>12.1</v>
       </c>
       <c r="S14" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
         <v>43.9</v>
       </c>
       <c r="U14" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W14" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
         <v>4.5</v>
@@ -2917,19 +2984,19 @@
         <v>20.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.7</v>
+        <v>102</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
         <v>3</v>
@@ -2938,7 +3005,7 @@
         <v>15</v>
       </c>
       <c r="AI14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
         <v>12</v>
@@ -2953,40 +3020,40 @@
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>9</v>
       </c>
       <c r="AP14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT14" t="n">
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -3027,22 +3094,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" t="n">
         <v>44</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>0.579</v>
+        <v>0.571</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J15" t="n">
         <v>83.09999999999999</v>
@@ -3057,10 +3124,10 @@
         <v>11.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="O15" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P15" t="n">
         <v>24</v>
@@ -3069,7 +3136,7 @@
         <v>0.752</v>
       </c>
       <c r="R15" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S15" t="n">
         <v>29.1</v>
@@ -3078,7 +3145,7 @@
         <v>40.9</v>
       </c>
       <c r="U15" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V15" t="n">
         <v>13.9</v>
@@ -3093,28 +3160,28 @@
         <v>6.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB15" t="n">
         <v>100.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>10</v>
       </c>
       <c r="AF15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
         <v>8</v>
@@ -3135,16 +3202,16 @@
         <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
         <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>7</v>
@@ -3156,7 +3223,7 @@
         <v>18</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>13</v>
@@ -3174,7 +3241,7 @@
         <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
         <v>11</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -3209,85 +3276,85 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" t="n">
         <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16" t="n">
-        <v>0.707</v>
+        <v>0.697</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J16" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.482</v>
+        <v>0.48</v>
       </c>
       <c r="L16" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M16" t="n">
         <v>18</v>
       </c>
       <c r="N16" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="O16" t="n">
         <v>21.6</v>
       </c>
       <c r="P16" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="R16" t="n">
         <v>9.6</v>
       </c>
       <c r="S16" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="T16" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="U16" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V16" t="n">
         <v>13.7</v>
       </c>
       <c r="W16" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
         <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>102.7</v>
+        <v>102.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3299,10 +3366,10 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI16" t="n">
         <v>19</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>15</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
@@ -3317,7 +3384,7 @@
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AO16" t="n">
         <v>3</v>
@@ -3332,31 +3399,31 @@
         <v>26</v>
       </c>
       <c r="AS16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV16" t="n">
         <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" t="n">
         <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>0.413</v>
+        <v>0.408</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,7 +3476,7 @@
         <v>34.2</v>
       </c>
       <c r="J17" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K17" t="n">
         <v>0.429</v>
@@ -3418,7 +3485,7 @@
         <v>5.9</v>
       </c>
       <c r="M17" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N17" t="n">
         <v>0.344</v>
@@ -3427,22 +3494,22 @@
         <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R17" t="n">
         <v>10.8</v>
       </c>
       <c r="S17" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T17" t="n">
         <v>41.1</v>
       </c>
       <c r="U17" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="V17" t="n">
         <v>13.5</v>
@@ -3457,7 +3524,7 @@
         <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA17" t="n">
         <v>20.9</v>
@@ -3469,19 +3536,19 @@
         <v>-1</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE17" t="n">
         <v>22</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
         <v>22</v>
       </c>
       <c r="AH17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
         <v>30</v>
@@ -3499,7 +3566,7 @@
         <v>19</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
         <v>27</v>
@@ -3508,16 +3575,16 @@
         <v>24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR17" t="n">
         <v>17</v>
       </c>
       <c r="AS17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU17" t="n">
         <v>30</v>
@@ -3526,16 +3593,16 @@
         <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
         <v>16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
         <v>16</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -3573,25 +3640,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>0.224</v>
+        <v>0.221</v>
       </c>
       <c r="H18" t="n">
         <v>48.2</v>
       </c>
       <c r="I18" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J18" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0.438</v>
@@ -3603,7 +3670,7 @@
         <v>19.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O18" t="n">
         <v>18.6</v>
@@ -3618,19 +3685,19 @@
         <v>13.4</v>
       </c>
       <c r="S18" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T18" t="n">
         <v>44.6</v>
       </c>
       <c r="U18" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V18" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="W18" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X18" t="n">
         <v>5.2</v>
@@ -3639,19 +3706,19 @@
         <v>5.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA18" t="n">
         <v>21.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>100.4</v>
+        <v>100.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3666,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>2</v>
@@ -3690,7 +3757,7 @@
         <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>1</v>
@@ -3702,7 +3769,7 @@
         <v>1</v>
       </c>
       <c r="AU18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV18" t="n">
         <v>30</v>
@@ -3714,19 +3781,19 @@
         <v>10</v>
       </c>
       <c r="AY18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB18" t="n">
         <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -3758,13 +3825,13 @@
         <v>75</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>0.293</v>
+        <v>0.307</v>
       </c>
       <c r="H19" t="n">
         <v>48.9</v>
@@ -3773,46 +3840,46 @@
         <v>35.3</v>
       </c>
       <c r="J19" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M19" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="O19" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P19" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0.758</v>
       </c>
       <c r="R19" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S19" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T19" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U19" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V19" t="n">
         <v>14.3</v>
       </c>
       <c r="W19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="X19" t="n">
         <v>4.7</v>
@@ -3827,13 +3894,13 @@
         <v>20</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.3</v>
+        <v>-6.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>25</v>
@@ -3863,31 +3930,31 @@
         <v>20</v>
       </c>
       <c r="AN19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO19" t="n">
         <v>25</v>
       </c>
-      <c r="AO19" t="n">
-        <v>24</v>
-      </c>
       <c r="AP19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR19" t="n">
         <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
         <v>30</v>
@@ -3899,7 +3966,7 @@
         <v>13</v>
       </c>
       <c r="AZ19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA19" t="n">
         <v>25</v>
@@ -3908,7 +3975,7 @@
         <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -3952,13 +4019,13 @@
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J20" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L20" t="n">
         <v>5.4</v>
@@ -3967,40 +4034,40 @@
         <v>15.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O20" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0.768</v>
       </c>
       <c r="R20" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S20" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T20" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U20" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
         <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z20" t="n">
         <v>20.9</v>
@@ -4009,25 +4076,25 @@
         <v>20.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
         <v>12</v>
       </c>
       <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
         <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>13</v>
       </c>
       <c r="AI20" t="n">
         <v>26</v>
@@ -4045,37 +4112,37 @@
         <v>25</v>
       </c>
       <c r="AN20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO20" t="n">
         <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ20" t="n">
         <v>13</v>
       </c>
       <c r="AR20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT20" t="n">
         <v>24</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>23</v>
       </c>
       <c r="AU20" t="n">
         <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
         <v>10</v>
       </c>
       <c r="AX20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY20" t="n">
         <v>19</v>
@@ -4087,7 +4154,7 @@
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC20" t="n">
         <v>14</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -4137,10 +4204,10 @@
         <v>38.3</v>
       </c>
       <c r="J21" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L21" t="n">
         <v>9.199999999999999</v>
@@ -4149,55 +4216,55 @@
         <v>24.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="O21" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="P21" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R21" t="n">
         <v>10.4</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T21" t="n">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W21" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y21" t="n">
         <v>4.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA21" t="n">
         <v>20.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>106.5</v>
+        <v>106.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>16</v>
@@ -4212,7 +4279,7 @@
         <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ21" t="n">
         <v>6</v>
@@ -4227,13 +4294,13 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP21" t="n">
         <v>8</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>6</v>
       </c>
       <c r="AQ21" t="n">
         <v>2</v>
@@ -4245,7 +4312,7 @@
         <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU21" t="n">
         <v>15</v>
@@ -4254,7 +4321,7 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E22" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F22" t="n">
         <v>26</v>
       </c>
       <c r="G22" t="n">
-        <v>0.653</v>
+        <v>0.658</v>
       </c>
       <c r="H22" t="n">
         <v>48.8</v>
       </c>
       <c r="I22" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J22" t="n">
         <v>80.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L22" t="n">
         <v>6</v>
@@ -4331,16 +4398,16 @@
         <v>17.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O22" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="P22" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.824</v>
+        <v>0.823</v>
       </c>
       <c r="R22" t="n">
         <v>10.9</v>
@@ -4352,7 +4419,7 @@
         <v>42.5</v>
       </c>
       <c r="U22" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V22" t="n">
         <v>14</v>
@@ -4367,19 +4434,19 @@
         <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB22" t="n">
         <v>104.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>7</v>
@@ -4394,13 +4461,13 @@
         <v>3</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL22" t="n">
         <v>18</v>
@@ -4421,13 +4488,13 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
         <v>10</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
         <v>23</v>
@@ -4439,13 +4506,13 @@
         <v>5</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -4486,19 +4553,19 @@
         <v>76</v>
       </c>
       <c r="E23" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>0.618</v>
+        <v>0.632</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J23" t="n">
         <v>78.40000000000001</v>
@@ -4510,16 +4577,16 @@
         <v>9.4</v>
       </c>
       <c r="M23" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O23" t="n">
         <v>17.7</v>
       </c>
       <c r="P23" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q23" t="n">
         <v>0.6899999999999999</v>
@@ -4528,40 +4595,40 @@
         <v>10.4</v>
       </c>
       <c r="S23" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.9</v>
+        <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
         <v>6.5</v>
       </c>
       <c r="X23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y23" t="n">
         <v>3.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
         <v>22</v>
       </c>
       <c r="AB23" t="n">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>8</v>
@@ -4573,7 +4640,7 @@
         <v>8</v>
       </c>
       <c r="AH23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
         <v>24</v>
@@ -4582,7 +4649,7 @@
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4591,13 +4658,13 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
         <v>21</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4606,16 +4673,16 @@
         <v>20</v>
       </c>
       <c r="AS23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
       </c>
       <c r="AU23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW23" t="n">
         <v>27</v>
@@ -4627,13 +4694,13 @@
         <v>3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC23" t="n">
         <v>6</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -4665,46 +4732,46 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E24" t="n">
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.526</v>
+        <v>0.519</v>
       </c>
       <c r="H24" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I24" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J24" t="n">
         <v>82.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M24" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="N24" t="n">
         <v>0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P24" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="R24" t="n">
         <v>10.4</v>
@@ -4713,7 +4780,7 @@
         <v>31.8</v>
       </c>
       <c r="T24" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U24" t="n">
         <v>22.8</v>
@@ -4728,7 +4795,7 @@
         <v>4.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z24" t="n">
         <v>19.6</v>
@@ -4737,16 +4804,16 @@
         <v>18.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF24" t="n">
         <v>15</v>
@@ -4773,22 +4840,22 @@
         <v>24</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
         <v>25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
         <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
@@ -4797,13 +4864,13 @@
         <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
@@ -4818,7 +4885,7 @@
         <v>14</v>
       </c>
       <c r="BC24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F25" t="n">
         <v>38</v>
       </c>
       <c r="G25" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H25" t="n">
         <v>48.8</v>
       </c>
       <c r="I25" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J25" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K25" t="n">
         <v>0.47</v>
       </c>
       <c r="L25" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O25" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P25" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>
@@ -4913,28 +4980,28 @@
         <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB25" t="n">
         <v>105.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
         <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>2</v>
@@ -4958,7 +5025,7 @@
         <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP25" t="n">
         <v>19</v>
@@ -4967,25 +5034,25 @@
         <v>17</v>
       </c>
       <c r="AR25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX25" t="n">
         <v>22</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>21</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
@@ -4994,7 +5061,7 @@
         <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -5029,58 +5096,58 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F26" t="n">
         <v>32</v>
       </c>
       <c r="G26" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>80.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L26" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.341</v>
+        <v>0.344</v>
       </c>
       <c r="O26" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="P26" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.802</v>
+        <v>0.8</v>
       </c>
       <c r="R26" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="S26" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="T26" t="n">
-        <v>38.9</v>
+        <v>39.3</v>
       </c>
       <c r="U26" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V26" t="n">
         <v>13.1</v>
@@ -5092,64 +5159,64 @@
         <v>4.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA26" t="n">
         <v>21.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF26" t="n">
         <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AM26" t="n">
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP26" t="n">
         <v>26</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AS26" t="n">
         <v>29</v>
@@ -5167,7 +5234,7 @@
         <v>4</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
         <v>4</v>
@@ -5176,7 +5243,7 @@
         <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
         <v>23</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -5238,22 +5305,22 @@
         <v>5.3</v>
       </c>
       <c r="M27" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O27" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="P27" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="R27" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S27" t="n">
         <v>30.7</v>
@@ -5271,25 +5338,25 @@
         <v>7.4</v>
       </c>
       <c r="X27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y27" t="n">
         <v>5.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.2</v>
+        <v>-5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5316,16 +5383,16 @@
         <v>25</v>
       </c>
       <c r="AM27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO27" t="n">
         <v>23</v>
       </c>
-      <c r="AO27" t="n">
-        <v>26</v>
-      </c>
       <c r="AP27" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AQ27" t="n">
         <v>28</v>
@@ -5346,10 +5413,10 @@
         <v>28</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY27" t="n">
         <v>21</v>
@@ -5358,10 +5425,10 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5478,7 @@
         <v>38.4</v>
       </c>
       <c r="J28" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K28" t="n">
         <v>0.474</v>
@@ -5420,28 +5487,28 @@
         <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.397</v>
+        <v>0.396</v>
       </c>
       <c r="O28" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="P28" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R28" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T28" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U28" t="n">
         <v>22.4</v>
@@ -5450,7 +5517,7 @@
         <v>13.6</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
         <v>4.6</v>
@@ -5462,16 +5529,16 @@
         <v>18.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.3</v>
+        <v>103.4</v>
       </c>
       <c r="AC28" t="n">
         <v>5.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
         <v>6</v>
@@ -5504,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP28" t="n">
         <v>18</v>
@@ -5519,16 +5586,16 @@
         <v>9</v>
       </c>
       <c r="AT28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
         <v>8</v>
       </c>
       <c r="AV28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW28" t="n">
         <v>9</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>13</v>
       </c>
       <c r="AX28" t="n">
         <v>18</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -5578,13 +5645,13 @@
         <v>75</v>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G29" t="n">
-        <v>0.28</v>
+        <v>0.267</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5593,10 +5660,10 @@
         <v>38.6</v>
       </c>
       <c r="J29" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.468</v>
+        <v>0.466</v>
       </c>
       <c r="L29" t="n">
         <v>4.3</v>
@@ -5605,7 +5672,7 @@
         <v>13.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0.319</v>
+        <v>0.317</v>
       </c>
       <c r="O29" t="n">
         <v>17.9</v>
@@ -5614,7 +5681,7 @@
         <v>23.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R29" t="n">
         <v>11.6</v>
@@ -5623,10 +5690,10 @@
         <v>28.5</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U29" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V29" t="n">
         <v>14.6</v>
@@ -5638,31 +5705,31 @@
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z29" t="n">
         <v>22</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>-6.2</v>
+        <v>-6.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH29" t="n">
         <v>19</v>
@@ -5671,7 +5738,7 @@
         <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK29" t="n">
         <v>8</v>
@@ -5692,13 +5759,13 @@
         <v>20</v>
       </c>
       <c r="AQ29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT29" t="n">
         <v>25</v>
@@ -5707,7 +5774,7 @@
         <v>10</v>
       </c>
       <c r="AV29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW29" t="n">
         <v>20</v>
@@ -5716,7 +5783,7 @@
         <v>25</v>
       </c>
       <c r="AY29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ29" t="n">
         <v>23</v>
@@ -5725,10 +5792,10 @@
         <v>26</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E30" t="n">
         <v>36</v>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G30" t="n">
-        <v>0.48</v>
+        <v>0.474</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J30" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L30" t="n">
         <v>5.3</v>
@@ -5787,31 +5854,31 @@
         <v>15.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.347</v>
+        <v>0.343</v>
       </c>
       <c r="O30" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="P30" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S30" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="T30" t="n">
-        <v>39.4</v>
+        <v>39.6</v>
       </c>
       <c r="U30" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V30" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W30" t="n">
         <v>7.6</v>
@@ -5820,25 +5887,25 @@
         <v>5.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.5</v>
+        <v>-1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5847,13 +5914,13 @@
         <v>18</v>
       </c>
       <c r="AH30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK30" t="n">
         <v>10</v>
@@ -5862,25 +5929,25 @@
         <v>24</v>
       </c>
       <c r="AM30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
         <v>9</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
         <v>27</v>
@@ -5889,13 +5956,13 @@
         <v>5</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>7</v>
       </c>
       <c r="AX30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
         <v>20</v>
@@ -5904,10 +5971,10 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
@@ -5942,52 +6009,52 @@
         <v>75</v>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G31" t="n">
-        <v>0.267</v>
+        <v>0.253</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J31" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K31" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="O31" t="n">
         <v>17.9</v>
       </c>
       <c r="P31" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q31" t="n">
         <v>0.746</v>
       </c>
       <c r="R31" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S31" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="U31" t="n">
         <v>19.6</v>
@@ -6005,19 +6072,19 @@
         <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA31" t="n">
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>97.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.5</v>
+        <v>-8</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6032,13 +6099,13 @@
         <v>5</v>
       </c>
       <c r="AI31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ31" t="n">
         <v>5</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>27</v>
@@ -6047,10 +6114,10 @@
         <v>26</v>
       </c>
       <c r="AN31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP31" t="n">
         <v>16</v>
@@ -6062,10 +6129,10 @@
         <v>3</v>
       </c>
       <c r="AS31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-3-2010-11</t>
+          <t>2011-04-03</t>
         </is>
       </c>
     </row>
